--- a/data/trans_orig/IP32-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>89318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78938</t>
+          <t>79079</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90074</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172307</t>
+          <t>172914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>186788</t>
+          <t>186896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>73204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82567</t>
+          <t>82629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64453</t>
+          <t>63784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141293</t>
+          <t>141544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>156431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54105</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62809</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86006</t>
+          <t>85744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94735</t>
+          <t>94664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143674</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>155685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176066</t>
+          <t>176321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>189091</t>
+          <t>189208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>177603</t>
+          <t>177427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190392</t>
+          <t>189512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>358139</t>
+          <t>358581</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>376565</t>
+          <t>375945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>82239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93949</t>
+          <t>93884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110345</t>
+          <t>110328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120662</t>
+          <t>120864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196761</t>
+          <t>197781</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212789</t>
+          <t>212328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>67825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73670</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57617</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>127839</t>
+          <t>127866</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139177</t>
+          <t>139128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37856</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49060</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>73252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>52025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58611</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>84208</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>565391</t>
+          <t>565145</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>589299</t>
+          <t>589932</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>598010</t>
+          <t>597542</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>623628</t>
+          <t>623451</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1168933</t>
+          <t>1171185</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1205151</t>
+          <t>1204540</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79654</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88110</t>
+          <t>88251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84891</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168821</t>
+          <t>168926</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177329</t>
+          <t>177248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86794</t>
+          <t>86348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92595</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86969</t>
+          <t>86375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>94907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176694</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186427</t>
+          <t>186297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81138</t>
+          <t>80784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165802</t>
+          <t>166079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172457</t>
+          <t>172451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190272</t>
+          <t>188710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200859</t>
+          <t>200746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208832</t>
+          <t>208596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220980</t>
+          <t>221140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>401360</t>
+          <t>403462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419301</t>
+          <t>419870</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126615</t>
+          <t>126867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139884</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124777</t>
+          <t>124751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>255170</t>
+          <t>255858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273629</t>
+          <t>273955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46200</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>52993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61549</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70928</t>
+          <t>71199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111136</t>
+          <t>109901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122588</t>
+          <t>122439</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36209</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37330</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62761</t>
+          <t>64915</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30722</t>
+          <t>30709</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>629719</t>
+          <t>630752</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>652502</t>
+          <t>652241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>669918</t>
+          <t>670468</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>690957</t>
+          <t>692123</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1308579</t>
+          <t>1308084</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1337269</t>
+          <t>1337458</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76076</t>
+          <t>75834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81849</t>
+          <t>81899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93145</t>
+          <t>93260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99797</t>
+          <t>99173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172144</t>
+          <t>171914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180329</t>
+          <t>180214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100008</t>
+          <t>99962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>105149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103387</t>
+          <t>103365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110593</t>
+          <t>110769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,47 +8317,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>211798</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>206314</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>214938</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>98,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>211798</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>206110</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>215053</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,42 +8738,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>72910</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68409</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74715</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>96,66%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72910</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>68710</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74715</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123344</t>
+          <t>123981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133719</t>
+          <t>133771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>210474</t>
+          <t>210418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220224</t>
+          <t>219979</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202345</t>
+          <t>202134</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>209634</t>
+          <t>209636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416596</t>
+          <t>415400</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>428217</t>
+          <t>428214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125447</t>
+          <t>125364</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133790</t>
+          <t>133681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128508</t>
+          <t>128346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139359</t>
+          <t>139420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>257159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270934</t>
+          <t>271170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59982</t>
+          <t>59897</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>62591</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117911</t>
+          <t>118874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127230</t>
+          <t>127203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28063</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>634433</t>
+          <t>634374</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>652719</t>
+          <t>652860</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>677711</t>
+          <t>678018</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>694598</t>
+          <t>695030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1319737</t>
+          <t>1319908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1343611</t>
+          <t>1343803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84372</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101065</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110338</t>
+          <t>108172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134353</t>
+          <t>134237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204153</t>
+          <t>205673</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233509</t>
+          <t>233866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>90941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94516</t>
+          <t>94521</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90901</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>95246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184085</t>
+          <t>183974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189240</t>
+          <t>189259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63236</t>
+          <t>63245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103447</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>114426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204613</t>
+          <t>203668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215301</t>
+          <t>214874</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210827</t>
+          <t>210801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>217130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418507</t>
+          <t>419232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>430913</t>
+          <t>431288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112329</t>
+          <t>112987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118515</t>
+          <t>118329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150932</t>
+          <t>150806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159810</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266708</t>
+          <t>267067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>277277</t>
+          <t>277268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67951</t>
+          <t>68051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>65974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71832</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130626</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>138912</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26551</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43236</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54932</t>
+          <t>55388</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>622304</t>
+          <t>622568</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>642747</t>
+          <t>642416</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>701155</t>
+          <t>703952</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>732420</t>
+          <t>732779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1335926</t>
+          <t>1335383</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1372012</t>
+          <t>1371178</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
